--- a/SGC-CKN/Excel/e0367dbc-b0e4-4f68-b22d-91960d56ac22_Thanh_Hoá_P1_117_D800_11-04-2026.xlsx
+++ b/SGC-CKN/Excel/e0367dbc-b0e4-4f68-b22d-91960d56ac22_Thanh_Hoá_P1_117_D800_11-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>09:40 11/04/2026</t>
+    <t>09:40 01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>20:31 11/04/2026</t>
+    <t>20:31 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">09:40
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">09:50
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:15
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:20
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:20
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">12:00
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:55
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">17:10
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,7 +176,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:31
-11/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>M1 Chuẩn; Sỏi Cao; Độ sâu 34,5</t>

--- a/SGC-CKN/Excel/e0367dbc-b0e4-4f68-b22d-91960d56ac22_Thanh_Hoá_P1_117_D800_11-04-2026.xlsx
+++ b/SGC-CKN/Excel/e0367dbc-b0e4-4f68-b22d-91960d56ac22_Thanh_Hoá_P1_117_D800_11-04-2026.xlsx
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">10:15
+    <t xml:space="preserve">10:05
 01/04/2026</t>
   </si>
   <si>
@@ -165,7 +165,7 @@
     <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">17:10
+    <t xml:space="preserve">17:00
 01/04/2026</t>
   </si>
   <si>
@@ -1148,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-1.9</v>
@@ -1157,10 +1157,10 @@
         <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="J11" s="8">
-        <v>7.14</v>
+        <v>11.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1189,13 +1189,13 @@
         <v>-5</v>
       </c>
       <c r="H12" s="9">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="9">
         <v>3.1</v>
       </c>
       <c r="J12" s="8">
-        <v>7.44</v>
+        <v>12.4</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1224,13 +1224,13 @@
         <v>-8.4</v>
       </c>
       <c r="H13" s="12">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="12">
         <v>3.4</v>
       </c>
       <c r="J13" s="8">
-        <v>40.8</v>
+        <v>13.6</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1326,16 +1326,16 @@
         <v>-22.4</v>
       </c>
       <c r="G16" s="21">
-        <v>-28.3</v>
+        <v>-26.3</v>
       </c>
       <c r="H16" s="21">
         <v>1.92</v>
       </c>
       <c r="I16" s="21">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="J16" s="24">
-        <v>3.08</v>
+        <v>2.03</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1358,19 +1358,19 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-28.3</v>
+        <v>-26.3</v>
       </c>
       <c r="G17" s="25">
         <v>-38</v>
       </c>
       <c r="H17" s="25">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="I17" s="25">
-        <v>9.7</v>
+        <v>11.7</v>
       </c>
       <c r="J17" s="24">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1399,13 +1399,13 @@
         <v>-44.44</v>
       </c>
       <c r="H18" s="28">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="I18" s="28">
         <v>6.44</v>
       </c>
       <c r="J18" s="24">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>52</v>
@@ -1560,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-1.9</v>
@@ -1569,10 +1569,10 @@
         <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="I2" s="8">
-        <v>7.14</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1595,13 +1595,13 @@
         <v>-5</v>
       </c>
       <c r="G3" s="9">
-        <v>0.42</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="9">
         <v>3.1</v>
       </c>
       <c r="I3" s="8">
-        <v>7.44</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1624,13 +1624,13 @@
         <v>-8.4</v>
       </c>
       <c r="G4" s="12">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="H4" s="12">
         <v>3.4</v>
       </c>
       <c r="I4" s="8">
-        <v>40.8</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1708,16 +1708,16 @@
         <v>-22.4</v>
       </c>
       <c r="F7" s="21">
-        <v>-28.3</v>
+        <v>-26.3</v>
       </c>
       <c r="G7" s="21">
         <v>1.92</v>
       </c>
       <c r="H7" s="21">
-        <v>5.9</v>
+        <v>3.9</v>
       </c>
       <c r="I7" s="24">
-        <v>3.08</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1734,19 +1734,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-28.3</v>
+        <v>-26.3</v>
       </c>
       <c r="F8" s="25">
         <v>-38</v>
       </c>
       <c r="G8" s="25">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="H8" s="25">
-        <v>9.7</v>
+        <v>11.7</v>
       </c>
       <c r="I8" s="24">
-        <v>2.98</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1769,13 +1769,13 @@
         <v>-44.44</v>
       </c>
       <c r="G9" s="28">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="H9" s="28">
         <v>6.44</v>
       </c>
       <c r="I9" s="24">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1792,7 +1792,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="33">
-        <v>-0.71</v>
+        <v>0</v>
       </c>
       <c r="F10" s="33">
         <v>-44.44</v>
@@ -1801,10 +1801,10 @@
         <v>10.85</v>
       </c>
       <c r="H10" s="33">
-        <v>43.73</v>
+        <v>44.44</v>
       </c>
       <c r="I10" s="33">
-        <v>4.03</v>
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
